--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F767"/>
+  <dimension ref="A1:F744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1824,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,19 +1888,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -2124,14 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>Continuing Jobless ClaimsDEC/28</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1848K</t>
+        </is>
+      </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2142,26 +2154,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,22 +2184,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>201K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>218K</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>213K</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2198,22 +2214,18 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2228,26 +2240,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>16.8M</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>16.5M</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>16.3M</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2332,22 +2332,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2380,19 +2376,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2406,22 +2398,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2432,18 +2420,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2454,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2476,18 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2498,15 +2494,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2886,26 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3054,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3092,26 +3084,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3122,22 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,22 +3226,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3252,26 +3256,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3282,18 +3282,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3308,10 +3308,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,12 +3330,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,22 +3558,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,7 +3584,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3596,10 +3592,14 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,18 +3704,18 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,26 +3730,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,18 +3970,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,12 +4304,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,22 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4352,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,22 +4374,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4418,22 +4418,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -4546,14 +4546,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -4582,22 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4612,18 +4612,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4634,18 +4642,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4660,17 +4672,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4679,7 +4691,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4690,16 +4702,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4712,24 +4728,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4742,18 +4750,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -4764,16 +4780,20 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4816,26 +4836,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4846,16 +4858,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,20 +4888,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4894,17 +4910,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -4913,7 +4929,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4924,22 +4940,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4954,26 +4966,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4984,22 +4988,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5014,20 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,17 +5040,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5070,22 +5070,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5100,26 +5100,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5378,22 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,26 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5464,22 +5460,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -5490,22 +5490,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -5994,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6024,22 +6028,18 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6176,15 +6176,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,22 +6224,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6312,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,22 +6404,22 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6616,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6646,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,22 +6736,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -6896,18 +6896,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6922,22 +6926,18 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -7204,26 +7204,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
           <t>4.3%</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7234,18 +7230,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7260,18 +7256,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,18 +7286,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7312,26 +7312,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,15 +7838,19 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>3</v>
@@ -7860,22 +7864,18 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -7886,22 +7886,18 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7912,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7934,18 +7930,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,22 +7956,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,26 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8126,22 +8126,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,22 +8156,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8186,18 +8182,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8212,22 +8208,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8242,18 +8234,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,22 +8260,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -8294,12 +8290,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8313,7 +8309,7 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -8324,22 +8320,26 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,18 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8628,22 +8632,18 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,26 +8658,14 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8688,18 +8676,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8714,22 +8706,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8744,22 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8774,26 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8804,14 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337">
@@ -8930,22 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -9016,22 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,15 +10002,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,12 +10028,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10038,22 +10050,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10064,19 +10072,15 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>3</v>
@@ -10090,12 +10094,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10112,22 +10116,18 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10494,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,18 +10520,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10542,18 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,22 +10572,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11290,22 +11286,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11316,18 +11308,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11338,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11364,18 +11356,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -11386,22 +11382,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11412,18 +11404,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11426,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -12006,14 +12006,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr"/>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12024,10 +12028,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr"/>
+          <t>42-Day Bill Auction</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>4.270%</t>
+        </is>
+      </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
@@ -12045,11 +12053,7 @@
           <t>52-Week Bill Auction</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
+      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
@@ -12064,18 +12068,14 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>4.270%</t>
-        </is>
-      </c>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483">
@@ -12217,11 +12217,7 @@
           <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
@@ -12236,14 +12232,10 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
@@ -12258,18 +12250,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12280,18 +12268,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12302,14 +12286,10 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12324,14 +12304,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12342,10 +12326,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
@@ -12360,14 +12348,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr"/>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -12378,10 +12370,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr"/>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
@@ -12396,10 +12392,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
@@ -12414,14 +12414,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12436,18 +12436,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12462,22 +12462,26 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -12488,22 +12492,26 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr"/>
+          <t>1.366M</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -12514,26 +12522,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12544,18 +12548,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12570,14 +12574,14 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12592,26 +12596,22 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
@@ -12792,22 +12792,22 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F516" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="517">
@@ -12818,16 +12818,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr"/>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E517" t="inlineStr"/>
       <c r="F517" t="n">
         <v>3</v>
       </c>
@@ -12840,14 +12836,22 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr"/>
-      <c r="E518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F518" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="519">
@@ -12858,7 +12862,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
@@ -12876,7 +12880,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -12894,18 +12898,14 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F521" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -12938,18 +12938,18 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F523" t="n">
@@ -13062,14 +13062,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -13098,14 +13098,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13224,14 +13224,14 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -13242,14 +13242,14 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
@@ -13468,18 +13468,22 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="551">
@@ -13490,18 +13494,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F551" t="n">
@@ -13516,22 +13520,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="553">
@@ -13542,18 +13546,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13568,22 +13572,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F555" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13883,19 +13883,19 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2025-02-25 14:50:00+05:30</t>
+          <t>2025-02-25 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Fed Logan Speech</t>
+          <t>Redbook YoYFEB/22</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -13919,19 +13919,27 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2025-02-25 19:25:00+05:30</t>
+          <t>2025-02-25 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/22</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F572" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -13942,14 +13950,18 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F573" t="n">
@@ -13964,18 +13976,14 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F574" t="n">
@@ -14012,14 +14020,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14034,14 +14042,14 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -14056,14 +14064,14 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F578" t="n">
@@ -14078,14 +14086,14 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -14100,22 +14108,18 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F580" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="581">
@@ -14143,23 +14147,27 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-25 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F582" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="583">
@@ -14170,18 +14178,22 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F583" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="584">
@@ -14214,18 +14226,18 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F585" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="586">
@@ -14236,22 +14248,18 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F586" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="587">
@@ -14262,18 +14270,14 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14288,14 +14292,14 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -14310,14 +14314,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14327,19 +14331,19 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2025-02-25 20:30:00+05:30</t>
+          <t>2025-02-25 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -14376,14 +14380,14 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -14415,34 +14419,30 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2025-02-25 21:00:00+05:30</t>
+          <t>2025-02-25 22:15:00+05:30</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr"/>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="E594" t="inlineStr"/>
       <c r="F594" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2025-02-25 22:15:00+05:30</t>
+          <t>2025-02-25 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -14455,19 +14455,19 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2025-02-25 22:15:00+05:30</t>
+          <t>2025-02-25 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr"/>
       <c r="F596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -14527,30 +14527,30 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2025-02-25 23:30:00+05:30</t>
+          <t>2025-02-26 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2025-02-25 23:30:00+05:30</t>
+          <t>2025-02-26 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -14563,55 +14563,55 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2025-02-25 23:30:00+05:30</t>
+          <t>2025-02-26 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2025-02-26 03:00:00+05:30</t>
+          <t>2025-02-26 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2025-02-26 03:00:00+05:30</t>
+          <t>2025-02-26 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14640,14 +14640,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -14658,14 +14658,14 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="608">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14730,14 +14730,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="612">
@@ -14748,14 +14748,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="613">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14779,71 +14779,75 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2025-02-26 17:30:00+05:30</t>
+          <t>2025-02-26 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2025-02-26 17:30:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2025-02-26 17:30:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2025-02-26 19:00:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
-      <c r="E617" t="inlineStr"/>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
       <c r="F617" t="n">
         <v>2</v>
       </c>
@@ -14851,12 +14855,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2025-02-26 19:00:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14874,18 +14878,14 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
+      <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F619" t="n">
@@ -14900,14 +14900,18 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -14917,12 +14921,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2025-02-26 20:30:00+05:30</t>
+          <t>2025-02-26 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -14935,67 +14939,55 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2025-02-26 20:30:00+05:30</t>
+          <t>2025-02-26 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr"/>
       <c r="F622" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2025-02-26 20:30:00+05:30</t>
+          <t>2025-02-26 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr"/>
-      <c r="E623" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
-        </is>
-      </c>
+      <c r="E623" t="inlineStr"/>
       <c r="F623" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2025-02-26 20:30:00+05:30</t>
+          <t>2025-02-26 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
-      <c r="E624" t="inlineStr">
-        <is>
-          <t>0.68M</t>
-        </is>
-      </c>
+      <c r="D624" t="inlineStr"/>
+      <c r="E624" t="inlineStr"/>
       <c r="F624" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="625">
@@ -15024,14 +15016,14 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
@@ -15042,7 +15034,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15060,7 +15052,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15078,7 +15070,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -15096,7 +15088,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -15114,7 +15106,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -15132,7 +15124,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15150,7 +15142,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15168,7 +15160,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15186,14 +15178,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15204,7 +15196,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15222,14 +15214,14 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr"/>
       <c r="F637" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638">
@@ -15258,7 +15250,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15276,25 +15268,25 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2025-02-26 21:00:00+05:30</t>
+          <t>2025-02-26 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -15307,12 +15299,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2025-02-26 21:00:00+05:30</t>
+          <t>2025-02-26 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15325,12 +15317,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2025-02-26 21:00:00+05:30</t>
+          <t>2025-02-26 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15343,12 +15335,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2025-02-26 21:00:00+05:30</t>
+          <t>2025-02-26 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15361,66 +15353,66 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2025-02-26 22:00:00+05:30</t>
+          <t>2025-02-26 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr"/>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2025-02-26 22:00:00+05:30</t>
+          <t>2025-02-26 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr"/>
       <c r="F646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2025-02-26 22:00:00+05:30</t>
+          <t>2025-02-26 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr"/>
       <c r="F647" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2025-02-26 22:00:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15433,73 +15425,85 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr"/>
-      <c r="E649" t="inlineStr"/>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F649" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr"/>
       <c r="F650" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
-      <c r="D651" t="inlineStr"/>
-      <c r="E651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F651" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -15510,18 +15514,14 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -15536,14 +15536,18 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr"/>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="F654" t="n">
@@ -15553,96 +15557,100 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr"/>
-      <c r="E655" t="inlineStr"/>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F655" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr"/>
       <c r="F656" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
       <c r="D657" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F657" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr"/>
-      <c r="E658" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E658" t="inlineStr"/>
       <c r="F658" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15660,22 +15668,14 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
-      <c r="D660" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E660" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D660" t="inlineStr"/>
+      <c r="E660" t="inlineStr"/>
       <c r="F660" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="661">
@@ -15686,16 +15686,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr"/>
-      <c r="E661" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E661" t="inlineStr"/>
       <c r="F661" t="n">
         <v>3</v>
       </c>
@@ -15708,12 +15704,20 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr"/>
-      <c r="E662" t="inlineStr"/>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F662" t="n">
         <v>3</v>
       </c>
@@ -15726,18 +15730,18 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -15752,14 +15756,14 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -15779,7 +15783,11 @@
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr"/>
-      <c r="E665" t="inlineStr"/>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F665" t="n">
         <v>3</v>
       </c>
@@ -15792,18 +15800,18 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -15818,22 +15826,18 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D667" t="inlineStr"/>
       <c r="E667" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F667" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="668">
@@ -15844,18 +15848,18 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -15870,22 +15874,18 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
-      <c r="D669" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D669" t="inlineStr"/>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F669" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="670">
@@ -15922,18 +15922,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -15948,18 +15948,22 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F672" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="673">
@@ -15970,18 +15974,22 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -15992,14 +16000,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F674" t="n">
@@ -16014,18 +16026,18 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -16040,16 +16052,12 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+      <c r="E676" t="inlineStr"/>
       <c r="F676" t="n">
         <v>3</v>
       </c>
@@ -16062,14 +16070,14 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -16110,16 +16118,12 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
-      <c r="E679" t="inlineStr">
-        <is>
-          <t>1874.0K</t>
-        </is>
-      </c>
+      <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
         <v>3</v>
       </c>
@@ -16132,46 +16136,34 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D681" t="inlineStr"/>
+      <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
         <v>2</v>
       </c>
@@ -16179,25 +16171,17 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E682" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D682" t="inlineStr"/>
+      <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
         <v>2</v>
       </c>
@@ -16205,25 +16189,17 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D683" t="inlineStr"/>
+      <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
         <v>2</v>
       </c>
@@ -16231,205 +16207,193 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+          <t>$50 million</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr"/>
-      <c r="E688" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr"/>
       <c r="F688" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr"/>
-      <c r="E689" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="E689" t="inlineStr"/>
       <c r="F689" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr"/>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
+      <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="F691" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2025-02-27 21:00:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E692" t="inlineStr"/>
+      <c r="D692" t="inlineStr"/>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F692" t="n">
         <v>3</v>
       </c>
@@ -16437,17 +16401,21 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2025-02-27 21:00:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
       <c r="D693" t="inlineStr"/>
-      <c r="E693" t="inlineStr"/>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F693" t="n">
         <v>3</v>
       </c>
@@ -16455,20 +16423,16 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2025-02-27 21:00:00+05:30</t>
+          <t>2025-02-27 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="n">
         <v>3</v>
@@ -16477,12 +16441,12 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2025-02-27 21:00:00+05:30</t>
+          <t>2025-02-27 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16495,21 +16459,17 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2025-02-27 21:30:00+05:30</t>
+          <t>2025-02-27 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
       <c r="D696" t="inlineStr"/>
-      <c r="E696" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="E696" t="inlineStr"/>
       <c r="F696" t="n">
         <v>3</v>
       </c>
@@ -16517,21 +16477,17 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2025-02-27 21:30:00+05:30</t>
+          <t>2025-02-27 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr"/>
-      <c r="E697" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="E697" t="inlineStr"/>
       <c r="F697" t="n">
         <v>3</v>
       </c>
@@ -16539,43 +16495,35 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2025-02-27 21:30:00+05:30</t>
+          <t>2025-02-27 22:15:00+05:30</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="E698" t="inlineStr"/>
       <c r="F698" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2025-02-27 21:30:00+05:30</t>
+          <t>2025-02-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
-      <c r="E699" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="E699" t="inlineStr"/>
       <c r="F699" t="n">
         <v>3</v>
       </c>
@@ -16583,12 +16531,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16601,12 +16549,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16619,12 +16567,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16637,30 +16585,30 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 23:45:00+05:30</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Fed Hammack Speech</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2025-02-27 22:15:00+05:30</t>
+          <t>2025-02-28 01:45:00+05:30</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Harker Speech</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16673,30 +16621,30 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2025-02-27 22:15:00+05:30</t>
+          <t>2025-02-28 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Balance SheetFEB/26</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2025-02-27 22:30:00+05:30</t>
+          <t>2025-02-28 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>Fed Balance SheetFEB/26</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16709,89 +16657,117 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2025-02-27 22:30:00+05:30</t>
+          <t>2025-02-28 08:45:00+05:30</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>Fed Goolsbee Speech</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr"/>
       <c r="F707" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2025-02-27 22:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
-      <c r="D708" t="inlineStr"/>
-      <c r="E708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F708" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2025-02-27 22:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
-      <c r="D709" t="inlineStr"/>
-      <c r="E709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F709" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2025-02-27 23:45:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Fed Hammack Speech</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
-      <c r="D710" t="inlineStr"/>
-      <c r="E710" t="inlineStr"/>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F710" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2025-02-27 23:45:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Fed Hammack Speech</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr"/>
-      <c r="E711" t="inlineStr"/>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F711" t="n">
         <v>2</v>
       </c>
@@ -16799,17 +16775,21 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2025-02-28 01:45:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Fed Harker Speech</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr"/>
-      <c r="E712" t="inlineStr"/>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F712" t="n">
         <v>2</v>
       </c>
@@ -16817,17 +16797,21 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2025-02-28 01:45:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Fed Harker Speech</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr"/>
-      <c r="E713" t="inlineStr"/>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F713" t="n">
         <v>2</v>
       </c>
@@ -16835,35 +16819,47 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2025-02-28 03:00:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/26</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
-      <c r="D714" t="inlineStr"/>
-      <c r="E714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>$ -116.0B</t>
+        </is>
+      </c>
       <c r="F714" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2025-02-28 03:00:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/26</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr"/>
-      <c r="E715" t="inlineStr"/>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F715" t="n">
         <v>3</v>
       </c>
@@ -16871,37 +16867,41 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2025-02-28 08:45:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Fed Goolsbee Speech</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2025-02-28 08:45:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Fed Goolsbee Speech</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F717" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="718">
@@ -16912,22 +16912,18 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F718" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="719">
@@ -16938,22 +16934,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E719" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D719" t="inlineStr"/>
+      <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -16964,20 +16952,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>$-114.7B</t>
-        </is>
-      </c>
-      <c r="E720" t="inlineStr">
-        <is>
-          <t>$ -116.0B</t>
-        </is>
-      </c>
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" t="inlineStr"/>
       <c r="F720" t="n">
         <v>2</v>
       </c>
@@ -16990,16 +16970,12 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr"/>
-      <c r="E721" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E721" t="inlineStr"/>
       <c r="F721" t="n">
         <v>2</v>
       </c>
@@ -17017,11 +16993,7 @@
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="E722" t="inlineStr"/>
       <c r="F722" t="n">
         <v>2</v>
       </c>
@@ -17034,18 +17006,18 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F723" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
@@ -17099,49 +17071,45 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Chicago PMIFEB</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F726" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Chicago PMIFEB</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F727" t="n">
@@ -17151,93 +17119,97 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E729" t="inlineStr"/>
       <c r="F729" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr"/>
       <c r="F730" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-03-03 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FinalFEB</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
-      <c r="D732" t="inlineStr"/>
-      <c r="E732" t="inlineStr"/>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>51.6</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>51.6</t>
+        </is>
+      </c>
       <c r="F732" t="n">
         <v>2</v>
       </c>
@@ -17245,59 +17217,63 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-03-03 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr"/>
-      <c r="E733" t="inlineStr"/>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
       <c r="F733" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-03-03 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F734" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-03-03 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F735" t="n">
@@ -17307,45 +17283,41 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>2025-02-28 20:15:00+05:30</t>
+          <t>2025-03-03 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Chicago PMIFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr"/>
       <c r="E736" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F736" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2025-02-28 20:15:00+05:30</t>
+          <t>2025-03-03 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Chicago PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
+      <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F737" t="n">
@@ -17355,12 +17327,12 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2025-02-28 23:30:00+05:30</t>
+          <t>2025-03-03 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17373,12 +17345,12 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2025-02-28 23:30:00+05:30</t>
+          <t>2025-03-03 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17391,12 +17363,12 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2025-02-28 23:30:00+05:30</t>
+          <t>2025-03-04 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Redbook YoYMAR/01</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17409,17 +17381,21 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2025-02-28 23:30:00+05:30</t>
+          <t>2025-03-04 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>RCM/TIPP Economic Optimism IndexMAR</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr"/>
-      <c r="E741" t="inlineStr"/>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="F741" t="n">
         <v>3</v>
       </c>
@@ -17427,540 +17403,58 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2025-03-03 20:15:00+05:30</t>
+          <t>2025-03-04 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FinalFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>51.6</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
-      </c>
+          <t>$50 million</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr"/>
       <c r="F742" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2025-03-03 20:15:00+05:30</t>
+          <t>2025-03-04 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FinalFEB</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
-      <c r="D743" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
-      </c>
-      <c r="E743" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
-      </c>
+      <c r="D743" t="inlineStr"/>
+      <c r="E743" t="inlineStr"/>
       <c r="F743" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2025-03-03 20:30:00+05:30</t>
+          <t>2025-03-05 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>API Crude Oil Stock ChangeFEB/28</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr"/>
-      <c r="E744" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E744" t="inlineStr"/>
       <c r="F744" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B745" t="inlineStr">
-        <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
-        </is>
-      </c>
-      <c r="C745" t="inlineStr"/>
-      <c r="D745" t="inlineStr"/>
-      <c r="E745" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="F745" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B746" t="inlineStr">
-        <is>
-          <t>ISM Manufacturing PMIFEB</t>
-        </is>
-      </c>
-      <c r="C746" t="inlineStr"/>
-      <c r="D746" t="inlineStr"/>
-      <c r="E746" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="F746" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B747" t="inlineStr">
-        <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
-        </is>
-      </c>
-      <c r="C747" t="inlineStr"/>
-      <c r="D747" t="inlineStr"/>
-      <c r="E747" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
-      <c r="F747" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B748" t="inlineStr">
-        <is>
-          <t>ISM Manufacturing PricesFEB</t>
-        </is>
-      </c>
-      <c r="C748" t="inlineStr"/>
-      <c r="D748" t="inlineStr"/>
-      <c r="E748" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="F748" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B749" t="inlineStr">
-        <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
-        </is>
-      </c>
-      <c r="C749" t="inlineStr"/>
-      <c r="D749" t="inlineStr"/>
-      <c r="E749" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="F749" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B750" t="inlineStr">
-        <is>
-          <t>Construction Spending MoMJAN</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr"/>
-      <c r="E750" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="F750" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B751" t="inlineStr">
-        <is>
-          <t>ISM Manufacturing PricesFEB</t>
-        </is>
-      </c>
-      <c r="C751" t="inlineStr"/>
-      <c r="D751" t="inlineStr"/>
-      <c r="E751" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="F751" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B752" t="inlineStr">
-        <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
-        </is>
-      </c>
-      <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr"/>
-      <c r="E752" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
-      <c r="F752" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>2025-03-03 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B753" t="inlineStr">
-        <is>
-          <t>ISM Manufacturing PMIFEB</t>
-        </is>
-      </c>
-      <c r="C753" t="inlineStr"/>
-      <c r="D753" t="inlineStr"/>
-      <c r="E753" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="F753" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>2025-03-03 22:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B754" t="inlineStr">
-        <is>
-          <t>6-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C754" t="inlineStr"/>
-      <c r="D754" t="inlineStr"/>
-      <c r="E754" t="inlineStr"/>
-      <c r="F754" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>2025-03-03 22:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B755" t="inlineStr">
-        <is>
-          <t>3-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C755" t="inlineStr"/>
-      <c r="D755" t="inlineStr"/>
-      <c r="E755" t="inlineStr"/>
-      <c r="F755" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>2025-03-03 22:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B756" t="inlineStr">
-        <is>
-          <t>6-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C756" t="inlineStr"/>
-      <c r="D756" t="inlineStr"/>
-      <c r="E756" t="inlineStr"/>
-      <c r="F756" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>2025-03-03 22:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B757" t="inlineStr">
-        <is>
-          <t>3-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
-      <c r="E757" t="inlineStr"/>
-      <c r="F757" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>2025-03-04 19:25:00+05:30</t>
-        </is>
-      </c>
-      <c r="B758" t="inlineStr">
-        <is>
-          <t>Redbook YoYMAR/01</t>
-        </is>
-      </c>
-      <c r="C758" t="inlineStr"/>
-      <c r="D758" t="inlineStr"/>
-      <c r="E758" t="inlineStr"/>
-      <c r="F758" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>2025-03-04 19:25:00+05:30</t>
-        </is>
-      </c>
-      <c r="B759" t="inlineStr">
-        <is>
-          <t>Redbook YoYMAR/01</t>
-        </is>
-      </c>
-      <c r="C759" t="inlineStr"/>
-      <c r="D759" t="inlineStr"/>
-      <c r="E759" t="inlineStr"/>
-      <c r="F759" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>2025-03-04 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B760" t="inlineStr">
-        <is>
-          <t>RCM/TIPP Economic Optimism IndexMAR</t>
-        </is>
-      </c>
-      <c r="C760" t="inlineStr"/>
-      <c r="D760" t="inlineStr"/>
-      <c r="E760" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F760" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
-        <is>
-          <t>2025-03-04 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B761" t="inlineStr">
-        <is>
-          <t>RCM/TIPP Economic Optimism IndexMAR</t>
-        </is>
-      </c>
-      <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr"/>
-      <c r="E761" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F761" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
-        <is>
-          <t>2025-03-04 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B762" t="inlineStr">
-        <is>
-          <t>LMI Logistics Managers IndexFEB</t>
-        </is>
-      </c>
-      <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr"/>
-      <c r="E762" t="inlineStr"/>
-      <c r="F762" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
-        <is>
-          <t>2025-03-04 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B763" t="inlineStr">
-        <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
-        </is>
-      </c>
-      <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E763" t="inlineStr"/>
-      <c r="F763" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
-        <is>
-          <t>2025-03-04 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B764" t="inlineStr">
-        <is>
-          <t>LMI Logistics Managers IndexFEB</t>
-        </is>
-      </c>
-      <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr"/>
-      <c r="F764" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
-        <is>
-          <t>2025-03-04 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B765" t="inlineStr">
-        <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
-        </is>
-      </c>
-      <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E765" t="inlineStr"/>
-      <c r="F765" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
-        <is>
-          <t>2025-03-05 03:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B766" t="inlineStr">
-        <is>
-          <t>API Crude Oil Stock ChangeFEB/28</t>
-        </is>
-      </c>
-      <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr"/>
-      <c r="E766" t="inlineStr"/>
-      <c r="F766" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
-        <is>
-          <t>2025-03-05 03:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B767" t="inlineStr">
-        <is>
-          <t>API Crude Oil Stock ChangeFEB/28</t>
-        </is>
-      </c>
-      <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
-      <c r="F767" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F744"/>
+  <dimension ref="A1:F767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,18 +1798,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1888,15 +1884,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -2124,26 +2124,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2154,26 +2142,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2184,26 +2172,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2214,18 +2198,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2240,14 +2228,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2332,18 +2332,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2354,12 +2358,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,15 +2380,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2398,18 +2406,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2420,22 +2432,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2454,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2476,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2494,19 +2498,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2886,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3054,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3084,26 +3092,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3122,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,26 +3226,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3256,22 +3252,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3282,18 +3282,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3308,14 +3308,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3330,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,18 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3584,7 +3588,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3592,14 +3596,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,18 +3704,18 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,18 +3970,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4326,22 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4374,18 +4370,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4418,22 +4418,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -4546,14 +4546,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -4582,22 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4612,26 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4642,22 +4634,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4672,17 +4660,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4691,7 +4679,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4702,20 +4690,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4728,16 +4712,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4750,26 +4742,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -4780,20 +4764,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4836,18 +4816,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4858,24 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4888,16 +4868,20 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4910,17 +4894,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -4929,7 +4913,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4940,18 +4924,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4966,18 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4988,22 +4984,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5018,16 +5014,20 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,17 +5040,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5070,22 +5070,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5100,26 +5100,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5378,22 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,22 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5460,26 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -5490,22 +5490,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,26 +5968,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5994,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6028,18 +6024,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6176,19 +6176,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6202,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6224,18 +6220,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,22 +6268,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -6316,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,22 +6404,22 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6646,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,22 +6736,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -6896,22 +6896,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6926,18 +6922,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -7204,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7230,18 +7234,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7256,22 +7260,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,18 +7286,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7312,26 +7312,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,19 +7838,15 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>3</v>
@@ -7864,18 +7860,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7886,18 +7886,22 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,22 +7934,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7956,22 +7956,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,26 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -8126,22 +8126,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,18 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,18 +8186,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8208,18 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,18 +8242,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8260,26 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8290,26 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -8320,26 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,22 +8572,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8602,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8632,18 +8628,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,14 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8676,22 +8688,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8706,22 +8714,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8736,22 +8744,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,22 +8774,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8792,26 +8804,14 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -8930,22 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,22 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -9012,26 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -10002,19 +9994,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10028,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10050,18 +10038,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10072,15 +10064,19 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>3</v>
@@ -10094,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,18 +10112,22 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10494,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,22 +10520,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,18 +10568,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,18 +11290,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -11308,22 +11316,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11334,18 +11338,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11356,22 +11364,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -11382,18 +11386,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11404,18 +11412,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11426,22 +11434,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -12006,18 +12006,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -12028,14 +12024,10 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>4.270%</t>
-        </is>
-      </c>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
@@ -12053,7 +12045,11 @@
           <t>52-Week Bill Auction</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr"/>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
@@ -12068,14 +12064,18 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr"/>
+          <t>42-Day Bill Auction</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>4.270%</t>
+        </is>
+      </c>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="483">
@@ -12217,7 +12217,11 @@
           <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr"/>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
@@ -12232,10 +12236,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
@@ -12250,14 +12258,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr"/>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -12268,14 +12280,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12286,10 +12302,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12304,18 +12324,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12326,14 +12342,10 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
@@ -12348,18 +12360,14 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12370,14 +12378,10 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
@@ -12392,14 +12396,10 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
@@ -12414,14 +12414,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12436,18 +12436,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12462,26 +12462,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12492,26 +12488,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -12522,22 +12514,26 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -12548,18 +12544,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12574,14 +12570,14 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12596,22 +12592,26 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr"/>
+          <t>1.366M</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
@@ -12792,22 +12792,22 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F516" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="517">
@@ -12818,12 +12818,16 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr"/>
-      <c r="E517" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F517" t="n">
         <v>3</v>
       </c>
@@ -12836,22 +12840,14 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr"/>
       <c r="F518" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="519">
@@ -12862,7 +12858,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
@@ -12880,7 +12876,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -12898,14 +12894,18 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F521" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -12938,18 +12938,18 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F523" t="n">
@@ -13062,14 +13062,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="530">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -13098,14 +13098,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13224,14 +13224,14 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -13242,14 +13242,14 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -13468,22 +13468,18 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -13494,18 +13490,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F551" t="n">
@@ -13520,22 +13516,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13546,18 +13542,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13572,18 +13568,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="555">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F555" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="556">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13883,19 +13883,19 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2025-02-25 19:25:00+05:30</t>
+          <t>2025-02-25 14:50:00+05:30</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/22</t>
+          <t>Fed Logan Speech</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="571">
@@ -13919,27 +13919,19 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-25 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>Redbook YoYFEB/22</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E572" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+      <c r="D572" t="inlineStr"/>
+      <c r="E572" t="inlineStr"/>
       <c r="F572" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="573">
@@ -13950,18 +13942,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F573" t="n">
@@ -13976,14 +13964,18 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F574" t="n">
@@ -14020,14 +14012,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14042,14 +14034,14 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -14064,14 +14056,14 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F578" t="n">
@@ -14086,14 +14078,14 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -14108,18 +14100,22 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F580" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="581">
@@ -14147,27 +14143,23 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2025-02-25 20:30:00+05:30</t>
+          <t>2025-02-25 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F582" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="583">
@@ -14178,22 +14170,18 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F583" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="584">
@@ -14226,18 +14214,18 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F585" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="586">
@@ -14248,18 +14236,22 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F586" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="587">
@@ -14270,14 +14262,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14292,14 +14288,14 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -14314,14 +14310,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14331,19 +14327,19 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2025-02-25 21:00:00+05:30</t>
+          <t>2025-02-25 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -14380,14 +14376,14 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -14419,30 +14415,34 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2025-02-25 22:15:00+05:30</t>
+          <t>2025-02-25 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr"/>
-      <c r="E594" t="inlineStr"/>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="F594" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2025-02-25 23:30:00+05:30</t>
+          <t>2025-02-25 22:15:00+05:30</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -14455,19 +14455,19 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2025-02-25 23:30:00+05:30</t>
+          <t>2025-02-25 22:15:00+05:30</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr"/>
       <c r="F596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -14527,30 +14527,30 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2025-02-26 03:00:00+05:30</t>
+          <t>2025-02-25 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/21</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2025-02-26 03:00:00+05:30</t>
+          <t>2025-02-25 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/21</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -14563,55 +14563,55 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2025-02-26 17:30:00+05:30</t>
+          <t>2025-02-25 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2025-02-26 17:30:00+05:30</t>
+          <t>2025-02-26 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2025-02-26 17:30:00+05:30</t>
+          <t>2025-02-26 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14640,14 +14640,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
@@ -14658,14 +14658,14 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="608">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14730,14 +14730,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14748,14 +14748,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14779,75 +14779,71 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2025-02-26 19:00:00+05:30</t>
+          <t>2025-02-26 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2025-02-26 20:30:00+05:30</t>
+          <t>2025-02-26 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2025-02-26 20:30:00+05:30</t>
+          <t>2025-02-26 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2025-02-26 20:30:00+05:30</t>
+          <t>2025-02-26 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
-      <c r="E617" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
-        </is>
-      </c>
+      <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
         <v>2</v>
       </c>
@@ -14855,12 +14851,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2025-02-26 20:30:00+05:30</t>
+          <t>2025-02-26 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14878,14 +14874,18 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="F619" t="n">
@@ -14900,18 +14900,14 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
-      <c r="D620" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
+      <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -14921,12 +14917,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2025-02-26 21:00:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -14939,55 +14935,67 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2025-02-26 21:00:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr"/>
       <c r="F622" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2025-02-26 21:00:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr"/>
-      <c r="E623" t="inlineStr"/>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
       <c r="F623" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2025-02-26 21:00:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
-      <c r="D624" t="inlineStr"/>
-      <c r="E624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>0.68M</t>
+        </is>
+      </c>
       <c r="F624" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="625">
@@ -15016,14 +15024,14 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="627">
@@ -15034,7 +15042,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15052,7 +15060,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15070,7 +15078,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -15088,7 +15096,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -15106,7 +15114,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -15124,7 +15132,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15142,7 +15150,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15160,7 +15168,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15178,14 +15186,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
@@ -15196,7 +15204,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15214,14 +15222,14 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr"/>
       <c r="F637" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="638">
@@ -15250,7 +15258,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15268,25 +15276,25 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2025-02-26 22:00:00+05:30</t>
+          <t>2025-02-26 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -15299,12 +15307,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2025-02-26 22:00:00+05:30</t>
+          <t>2025-02-26 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15317,12 +15325,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2025-02-26 22:00:00+05:30</t>
+          <t>2025-02-26 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15335,12 +15343,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15353,66 +15361,66 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr"/>
       <c r="F645" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr"/>
       <c r="F646" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr"/>
       <c r="F647" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-26 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15425,85 +15433,73 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-26 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr"/>
-      <c r="E649" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E649" t="inlineStr"/>
       <c r="F649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-26 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr"/>
       <c r="F650" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-26 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
-      <c r="D651" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E651" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D651" t="inlineStr"/>
+      <c r="E651" t="inlineStr"/>
       <c r="F651" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2025-02-26 23:30:00+05:30</t>
+          <t>2025-02-26 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -15514,14 +15510,18 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -15536,18 +15536,14 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F654" t="n">
@@ -15557,100 +15553,96 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E655" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D655" t="inlineStr"/>
+      <c r="E655" t="inlineStr"/>
       <c r="F655" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr"/>
       <c r="F656" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
       <c r="D657" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="F657" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr"/>
-      <c r="E658" t="inlineStr"/>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F658" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2025-02-27 19:00:00+05:30</t>
+          <t>2025-02-26 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15668,14 +15660,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
-      <c r="D660" t="inlineStr"/>
-      <c r="E660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F660" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="661">
@@ -15686,12 +15686,16 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr"/>
-      <c r="E661" t="inlineStr"/>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F661" t="n">
         <v>3</v>
       </c>
@@ -15704,20 +15708,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E662" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" t="inlineStr"/>
       <c r="F662" t="n">
         <v>3</v>
       </c>
@@ -15730,18 +15726,18 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -15756,14 +15752,14 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -15783,11 +15779,7 @@
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr"/>
-      <c r="E665" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="E665" t="inlineStr"/>
       <c r="F665" t="n">
         <v>3</v>
       </c>
@@ -15800,18 +15792,18 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -15826,18 +15818,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F667" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="668">
@@ -15848,18 +15844,18 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -15874,18 +15870,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
-      <c r="D669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F669" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670">
@@ -15922,18 +15922,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -15948,22 +15948,18 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F672" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="673">
@@ -15974,22 +15970,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="674">
@@ -16000,18 +15992,14 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F674" t="n">
@@ -16026,18 +16014,18 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -16052,12 +16040,16 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="F676" t="n">
         <v>3</v>
       </c>
@@ -16070,14 +16062,14 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -16118,12 +16110,16 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
-      <c r="E679" t="inlineStr"/>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>1874.0K</t>
+        </is>
+      </c>
       <c r="F679" t="n">
         <v>3</v>
       </c>
@@ -16136,34 +16132,46 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F680" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr"/>
-      <c r="E681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F681" t="n">
         <v>2</v>
       </c>
@@ -16171,17 +16179,25 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr"/>
-      <c r="E682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F682" t="n">
         <v>2</v>
       </c>
@@ -16189,17 +16205,25 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
-      <c r="E683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F683" t="n">
         <v>2</v>
       </c>
@@ -16207,193 +16231,205 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F684" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2025-02-27 20:30:00+05:30</t>
+          <t>2025-02-27 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2025-02-27 21:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr"/>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="F686" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2025-02-27 21:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2025-02-27 21:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr"/>
+      <c r="D688" t="inlineStr"/>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="F688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2025-02-27 21:00:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr"/>
-      <c r="E689" t="inlineStr"/>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="F689" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2025-02-27 21:30:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2025-02-27 21:30:00+05:30</t>
+          <t>2025-02-27 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F691" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2025-02-27 21:30:00+05:30</t>
+          <t>2025-02-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr"/>
-      <c r="E692" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr"/>
       <c r="F692" t="n">
         <v>3</v>
       </c>
@@ -16401,21 +16437,17 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2025-02-27 21:30:00+05:30</t>
+          <t>2025-02-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
       <c r="D693" t="inlineStr"/>
-      <c r="E693" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="E693" t="inlineStr"/>
       <c r="F693" t="n">
         <v>3</v>
       </c>
@@ -16423,16 +16455,20 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="n">
         <v>3</v>
@@ -16441,12 +16477,12 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16459,17 +16495,21 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
       <c r="D696" t="inlineStr"/>
-      <c r="E696" t="inlineStr"/>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F696" t="n">
         <v>3</v>
       </c>
@@ -16477,17 +16517,21 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr"/>
-      <c r="E697" t="inlineStr"/>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F697" t="n">
         <v>3</v>
       </c>
@@ -16495,35 +16539,43 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2025-02-27 22:15:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr"/>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2025-02-27 22:30:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
-      <c r="E699" t="inlineStr"/>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F699" t="n">
         <v>3</v>
       </c>
@@ -16531,12 +16583,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2025-02-27 22:30:00+05:30</t>
+          <t>2025-02-27 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16549,12 +16601,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2025-02-27 22:30:00+05:30</t>
+          <t>2025-02-27 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16567,12 +16619,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2025-02-27 22:30:00+05:30</t>
+          <t>2025-02-27 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16585,30 +16637,30 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2025-02-27 23:45:00+05:30</t>
+          <t>2025-02-27 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Fed Hammack Speech</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2025-02-28 01:45:00+05:30</t>
+          <t>2025-02-27 22:15:00+05:30</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Fed Harker Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16621,30 +16673,30 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2025-02-28 03:00:00+05:30</t>
+          <t>2025-02-27 22:15:00+05:30</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/26</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2025-02-28 03:00:00+05:30</t>
+          <t>2025-02-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/26</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16657,117 +16709,89 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2025-02-28 08:45:00+05:30</t>
+          <t>2025-02-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Fed Goolsbee Speech</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr"/>
       <c r="F707" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
-      <c r="D708" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E708" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D708" t="inlineStr"/>
+      <c r="E708" t="inlineStr"/>
       <c r="F708" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
-      <c r="D709" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E709" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="inlineStr"/>
       <c r="F709" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-27 23:45:00+05:30</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Fed Hammack Speech</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
-      <c r="D710" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E710" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D710" t="inlineStr"/>
+      <c r="E710" t="inlineStr"/>
       <c r="F710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-27 23:45:00+05:30</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Fed Hammack Speech</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr"/>
-      <c r="E711" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E711" t="inlineStr"/>
       <c r="F711" t="n">
         <v>2</v>
       </c>
@@ -16775,21 +16799,17 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 01:45:00+05:30</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Fed Harker Speech</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr"/>
-      <c r="E712" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="E712" t="inlineStr"/>
       <c r="F712" t="n">
         <v>2</v>
       </c>
@@ -16797,21 +16817,17 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 01:45:00+05:30</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Fed Harker Speech</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr"/>
-      <c r="E713" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E713" t="inlineStr"/>
       <c r="F713" t="n">
         <v>2</v>
       </c>
@@ -16819,47 +16835,35 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Fed Balance SheetFEB/26</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
-      <c r="D714" t="inlineStr">
-        <is>
-          <t>$-114.7B</t>
-        </is>
-      </c>
-      <c r="E714" t="inlineStr">
-        <is>
-          <t>$ -116.0B</t>
-        </is>
-      </c>
+      <c r="D714" t="inlineStr"/>
+      <c r="E714" t="inlineStr"/>
       <c r="F714" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Fed Balance SheetFEB/26</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr"/>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="E715" t="inlineStr"/>
       <c r="F715" t="n">
         <v>3</v>
       </c>
@@ -16867,41 +16871,37 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 08:45:00+05:30</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Fed Goolsbee Speech</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2025-02-28 19:00:00+05:30</t>
+          <t>2025-02-28 08:45:00+05:30</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Fed Goolsbee Speech</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E717" t="inlineStr"/>
       <c r="F717" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="718">
@@ -16912,18 +16912,22 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F718" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="719">
@@ -16934,14 +16938,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr"/>
-      <c r="E719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F719" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
@@ -16952,12 +16964,20 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr"/>
-      <c r="E720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>$ -116.0B</t>
+        </is>
+      </c>
       <c r="F720" t="n">
         <v>2</v>
       </c>
@@ -16970,12 +16990,16 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr"/>
-      <c r="E721" t="inlineStr"/>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F721" t="n">
         <v>2</v>
       </c>
@@ -16993,7 +17017,11 @@
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr"/>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F722" t="n">
         <v>2</v>
       </c>
@@ -17006,18 +17034,18 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F723" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="724">
@@ -17071,45 +17099,49 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>2025-02-28 20:15:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Chicago PMIFEB</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F726" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2025-02-28 20:15:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Chicago PMIFEB</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F727" t="n">
@@ -17119,97 +17151,93 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2025-02-28 23:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>2025-02-28 23:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr"/>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F729" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>2025-02-28 23:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr"/>
       <c r="F730" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>2025-02-28 23:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2025-03-03 20:15:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FinalFEB</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
-      <c r="D732" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
-      </c>
-      <c r="E732" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
-      </c>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" t="inlineStr"/>
       <c r="F732" t="n">
         <v>2</v>
       </c>
@@ -17217,63 +17245,59 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>2025-03-03 20:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr"/>
-      <c r="E733" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
+      <c r="E733" t="inlineStr"/>
       <c r="F733" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>2025-03-03 20:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F734" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2025-03-03 20:30:00+05:30</t>
+          <t>2025-02-28 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F735" t="n">
@@ -17283,41 +17307,45 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>2025-03-03 20:30:00+05:30</t>
+          <t>2025-02-28 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>Chicago PMIFEB</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr"/>
       <c r="E736" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F736" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2025-03-03 20:30:00+05:30</t>
+          <t>2025-02-28 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>Chicago PMIFEB</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr"/>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F737" t="n">
@@ -17327,12 +17355,12 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2025-03-03 22:00:00+05:30</t>
+          <t>2025-02-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17345,12 +17373,12 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2025-03-03 22:00:00+05:30</t>
+          <t>2025-02-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17363,12 +17391,12 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2025-03-04 19:25:00+05:30</t>
+          <t>2025-02-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Redbook YoYMAR/01</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17381,21 +17409,17 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2025-03-04 20:30:00+05:30</t>
+          <t>2025-02-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>RCM/TIPP Economic Optimism IndexMAR</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr"/>
-      <c r="E741" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="E741" t="inlineStr"/>
       <c r="F741" t="n">
         <v>3</v>
       </c>
@@ -17403,58 +17427,540 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2025-03-04 21:00:00+05:30</t>
+          <t>2025-03-03 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>S&amp;P Global Manufacturing PMI FinalFEB</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr"/>
+          <t>51.6</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>51.6</t>
+        </is>
+      </c>
       <c r="F742" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2025-03-04 21:00:00+05:30</t>
+          <t>2025-03-03 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FinalFEB</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
-      <c r="D743" t="inlineStr"/>
-      <c r="E743" t="inlineStr"/>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>51.6</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>51.6</t>
+        </is>
+      </c>
       <c r="F743" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2025-03-05 03:00:00+05:30</t>
+          <t>2025-03-03 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/28</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr"/>
-      <c r="E744" t="inlineStr"/>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F744" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing New OrdersFEB</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr"/>
+      <c r="D745" t="inlineStr"/>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="F745" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing PMIFEB</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr"/>
+      <c r="D746" t="inlineStr"/>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F746" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing EmploymentFEB</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr"/>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="F747" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing PricesFEB</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr"/>
+      <c r="D748" t="inlineStr"/>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F748" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing New OrdersFEB</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr"/>
+      <c r="D749" t="inlineStr"/>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="F749" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Construction Spending MoMJAN</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr"/>
+      <c r="D750" t="inlineStr"/>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F750" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing PricesFEB</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr"/>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F751" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing EmploymentFEB</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr"/>
+      <c r="D752" t="inlineStr"/>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="F752" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2025-03-03 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing PMIFEB</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr"/>
+      <c r="D753" t="inlineStr"/>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F753" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2025-03-03 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr"/>
+      <c r="D754" t="inlineStr"/>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2025-03-03 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr"/>
+      <c r="D755" t="inlineStr"/>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2025-03-03 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr"/>
+      <c r="D756" t="inlineStr"/>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2025-03-03 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr"/>
+      <c r="D757" t="inlineStr"/>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2025-03-04 19:25:00+05:30</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Redbook YoYMAR/01</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr"/>
+      <c r="D758" t="inlineStr"/>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2025-03-04 19:25:00+05:30</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Redbook YoYMAR/01</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr"/>
+      <c r="D759" t="inlineStr"/>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2025-03-04 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>RCM/TIPP Economic Optimism IndexMAR</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr"/>
+      <c r="D760" t="inlineStr"/>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F760" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2025-03-04 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>RCM/TIPP Economic Optimism IndexMAR</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr"/>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F761" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2025-03-04 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>LMI Logistics Managers IndexFEB</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr"/>
+      <c r="D762" t="inlineStr"/>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2025-03-04 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2025-03-04 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>LMI Logistics Managers IndexFEB</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr"/>
+      <c r="D764" t="inlineStr"/>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2025-03-04 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2025-03-05 03:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr"/>
+      <c r="D766" t="inlineStr"/>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2025-03-05 03:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr"/>
+      <c r="D767" t="inlineStr"/>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,15 +1798,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1824,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1888,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2124,14 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2142,26 +2154,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,18 +2180,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2198,26 +2210,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2228,26 +2228,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2332,22 +2332,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2380,19 +2376,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2406,22 +2398,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2432,12 +2420,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2454,15 +2442,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2476,12 +2468,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2498,18 +2490,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2520,18 +2516,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2886,26 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2912,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2938,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3122,22 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,26 +3252,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3282,22 +3278,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3308,10 +3308,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,12 +3330,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3682,14 +3682,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,18 +3700,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,26 +3730,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3970,18 +3970,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,22 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,22 +4370,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4396,12 +4392,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4418,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4444,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,18 +4462,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -4546,14 +4546,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -4582,22 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4612,18 +4612,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4634,18 +4642,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4660,17 +4672,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4679,7 +4691,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4690,16 +4702,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4712,24 +4728,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4742,18 +4750,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -4764,16 +4780,20 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4816,26 +4836,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4846,16 +4858,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,20 +4888,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4894,17 +4910,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -4913,7 +4929,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4924,22 +4940,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4954,26 +4966,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4984,22 +4988,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5014,20 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5070,26 +5070,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5378,22 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,26 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5464,22 +5460,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -5490,22 +5490,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,18 +5968,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -5994,26 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6024,26 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,22 +6220,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6312,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,18 +6360,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6382,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,19 +6408,15 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>3</v>
@@ -6560,22 +6560,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="n">
@@ -6590,26 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6616,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6646,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -6896,18 +6896,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6922,22 +6926,18 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -7204,26 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7234,18 +7234,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7260,22 +7260,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -7286,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7312,22 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,22 +7860,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -7886,22 +7886,18 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7912,18 +7908,22 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -7934,18 +7934,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,19 +7960,15 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>3</v>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,26 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8126,26 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8156,26 +8148,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8186,18 +8178,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8212,26 +8204,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -8242,18 +8234,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,18 +8260,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,22 +8290,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,18 +8320,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,22 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8598,22 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,22 +8632,18 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,26 +8658,14 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8688,18 +8676,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8714,26 +8706,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8744,22 +8736,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8774,22 +8762,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8804,14 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337">
@@ -8930,22 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -9016,22 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,18 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,12 +10002,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10016,15 +10024,19 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>3</v>
@@ -10038,22 +10050,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10064,19 +10072,15 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>3</v>
@@ -10090,12 +10094,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10112,22 +10116,18 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10494,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,18 +10520,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10542,18 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,22 +10572,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11290,22 +11286,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11316,18 +11308,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11338,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11364,18 +11356,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -11386,22 +11378,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11412,18 +11400,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11426,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -12006,14 +12006,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr"/>
+          <t>42-Day Bill Auction</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>4.270%</t>
+        </is>
+      </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12027,7 +12031,11 @@
           <t>52-Week Bill Auction</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
@@ -12042,18 +12050,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -12064,14 +12068,10 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>4.270%</t>
-        </is>
-      </c>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
@@ -12214,18 +12214,14 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -12236,14 +12232,10 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
@@ -12258,14 +12250,10 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
@@ -12280,18 +12268,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12302,14 +12286,10 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12324,14 +12304,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12342,10 +12326,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
@@ -12360,14 +12348,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr"/>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -12378,10 +12370,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
@@ -12399,7 +12395,11 @@
           <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr"/>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
@@ -12414,14 +12414,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12436,18 +12436,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12462,22 +12462,26 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -12488,22 +12492,26 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr"/>
+          <t>1.366M</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -12514,26 +12522,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12544,18 +12548,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12570,14 +12574,14 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12592,26 +12596,22 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
@@ -12792,18 +12792,18 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F516" t="n">
@@ -12818,14 +12818,18 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F517" t="n">
@@ -12840,7 +12844,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
@@ -12858,7 +12862,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
@@ -12876,12 +12880,16 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
       <c r="D520" t="inlineStr"/>
-      <c r="E520" t="inlineStr"/>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F520" t="n">
         <v>3</v>
       </c>
@@ -12894,22 +12902,22 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F521" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -12920,7 +12928,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -12938,22 +12946,14 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E523" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr"/>
       <c r="F523" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="524">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -13080,14 +13080,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13098,14 +13098,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,14 +13188,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13242,14 +13242,14 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="550">
@@ -13468,18 +13468,22 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="551">
@@ -13490,18 +13494,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F551" t="n">
@@ -13516,22 +13520,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13542,18 +13546,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13568,22 +13572,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F555" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -14034,14 +14034,14 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -14056,14 +14056,14 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F578" t="n">
@@ -14078,18 +14078,18 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F579" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="580">
@@ -14126,18 +14126,18 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F581" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="582">
@@ -14148,14 +14148,14 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F582" t="n">
@@ -14174,7 +14174,11 @@
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr">
         <is>
           <t>103</t>
@@ -14514,14 +14518,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -14568,14 +14572,14 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14640,7 +14644,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14658,14 +14662,14 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="608">
@@ -14676,7 +14680,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14712,14 +14716,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14820,7 +14824,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14922,7 +14926,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -14940,7 +14944,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
@@ -15024,14 +15028,14 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
@@ -15042,7 +15046,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15060,7 +15064,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15096,7 +15100,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -15114,14 +15118,14 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr"/>
       <c r="F631" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="632">
@@ -15132,7 +15136,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15168,7 +15172,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15312,7 +15316,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15456,7 +15460,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15492,7 +15496,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15510,20 +15514,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" t="inlineStr"/>
       <c r="F653" t="n">
         <v>3</v>
       </c>
@@ -15558,12 +15554,20 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr"/>
-      <c r="E655" t="inlineStr"/>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F655" t="n">
         <v>3</v>
       </c>
@@ -15642,7 +15646,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15708,12 +15712,20 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr"/>
-      <c r="E662" t="inlineStr"/>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F662" t="n">
         <v>3</v>
       </c>
@@ -15726,22 +15738,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F663" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -15752,18 +15764,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F664" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="665">
@@ -15774,14 +15790,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr"/>
-      <c r="E665" t="inlineStr"/>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>225.0K</t>
+        </is>
+      </c>
       <c r="F665" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="666">
@@ -15792,18 +15816,14 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D666" t="inlineStr"/>
       <c r="E666" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -15818,22 +15838,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F667" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="668">
@@ -15844,22 +15864,18 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D668" t="inlineStr"/>
       <c r="E668" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F668" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="669">
@@ -15870,22 +15886,18 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
-      <c r="D669" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D669" t="inlineStr"/>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F669" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="670">
@@ -15896,22 +15908,18 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
-      <c r="D670" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
+      <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F670" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="671">
@@ -15948,18 +15956,22 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F672" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673">
@@ -15970,16 +15982,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+      <c r="E673" t="inlineStr"/>
       <c r="F673" t="n">
         <v>3</v>
       </c>
@@ -16062,14 +16070,18 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr"/>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -16210,22 +16222,22 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="684">
@@ -16288,20 +16300,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
-      <c r="D686" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D686" t="inlineStr"/>
+      <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
         <v>2</v>
       </c>
@@ -16332,14 +16336,18 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F688" t="n">
@@ -16376,12 +16384,16 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr"/>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="F690" t="n">
         <v>2</v>
       </c>
@@ -16500,7 +16512,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16566,7 +16578,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16732,7 +16744,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16750,7 +16762,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -17130,22 +17142,18 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F727" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="728">
@@ -17156,14 +17164,22 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr"/>
-      <c r="E728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F728" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="729">
@@ -17174,16 +17190,12 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E729" t="inlineStr"/>
       <c r="F729" t="n">
         <v>1</v>
       </c>
@@ -17196,14 +17208,18 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr"/>
-      <c r="E730" t="inlineStr"/>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F730" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="731">
@@ -17214,7 +17230,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17232,7 +17248,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17250,7 +17266,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -17268,18 +17284,14 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr"/>
-      <c r="E734" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E734" t="inlineStr"/>
       <c r="F734" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="735">
@@ -17316,7 +17328,11 @@
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
-      <c r="D736" t="inlineStr"/>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
       <c r="E736" t="inlineStr">
         <is>
           <t>42</t>
@@ -17360,7 +17376,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17378,7 +17394,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17528,18 +17544,18 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="747">
@@ -17550,18 +17566,18 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F747" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748">
@@ -17722,7 +17738,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -17740,7 +17756,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
@@ -17856,11 +17872,15 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr"/>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
         <v>3</v>
@@ -17874,15 +17894,11 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
         <v>3</v>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F767"/>
+  <dimension ref="A1:F772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,19 +816,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,22 +838,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -864,15 +860,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,22 +886,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,18 +930,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1608,18 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1634,22 +1634,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1660,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2202,22 +2202,18 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>16.8M</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>16.5M</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2232,18 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,22 +2354,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2380,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2406,15 +2398,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2428,19 +2424,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3</v>
@@ -2454,18 +2446,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2476,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/09</t>
+          <t>30-Year Mortgage RateJAN/09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/09</t>
+          <t>15-Year Mortgage RateJAN/09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2886,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3308,10 +3308,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3558,22 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,22 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3659,11 +3659,11 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3674,18 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3700,26 +3704,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3730,7 +3734,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3738,14 +3742,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,18 +4014,18 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4326,22 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4374,18 +4370,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4418,22 +4418,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4612,16 +4612,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4634,22 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4660,26 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4690,16 +4698,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4712,22 +4728,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4742,12 +4754,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4764,18 +4776,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4786,7 +4806,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4796,16 +4816,16 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4816,26 +4836,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4846,12 +4858,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4868,18 +4880,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -4894,26 +4910,18 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -4954,26 +4962,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4988,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,18 +5010,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5740,18 +5740,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5784,12 +5784,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5806,18 +5806,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5968,26 +5968,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5994,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6028,18 +6024,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -6176,22 +6176,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,18 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,15 +6246,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6338,18 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6360,19 +6364,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6620,22 +6616,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6646,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>4.24M</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7342,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,18 +7368,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7398,26 +7398,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,18 +7620,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -7816,15 +7816,19 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>3</v>
@@ -7838,18 +7842,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7860,12 +7868,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,22 +7890,18 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7908,18 +7912,22 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -7930,19 +7938,15 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>3</v>
@@ -7956,12 +7960,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,12 +7982,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8000,22 +8004,18 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -8096,22 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8126,26 +8122,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8156,26 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -8186,18 +8182,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8212,18 +8208,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,22 +8234,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -8264,26 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8294,18 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8320,26 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/30</t>
+          <t>30-Year Mortgage RateJAN/30</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/30</t>
+          <t>15-Year Mortgage RateJAN/30</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>6.12%</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -8852,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8878,15 +8874,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,22 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,26 +9046,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,18 +9498,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,18 +9542,18 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,18 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9972,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,22 +9998,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -10020,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,22 +10046,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,22 +10090,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,14 +10396,14 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,14 +10432,14 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,18 +10902,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,22 +10924,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -10954,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
@@ -10976,14 +10976,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,22 +11002,18 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -11050,22 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11076,14 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11290,22 +11286,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11316,14 +11308,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -11338,14 +11330,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -11360,22 +11356,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -11386,18 +11382,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11412,14 +11404,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11434,18 +11426,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
@@ -11911,11 +11911,7 @@
           <t>6-Month Bill Auction</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>4.220%</t>
-        </is>
-      </c>
+      <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="n">
@@ -11930,10 +11926,14 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr"/>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>4.225%</t>
+        </is>
+      </c>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr"/>
       <c r="F475" t="n">
@@ -11948,14 +11948,10 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>4.225%</t>
-        </is>
-      </c>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr"/>
       <c r="F476" t="n">
@@ -11970,10 +11966,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr"/>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>4.220%</t>
+        </is>
+      </c>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr"/>
       <c r="F477" t="n">
@@ -12089,7 +12089,11 @@
           <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr"/>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>$87.1B</t>
+        </is>
+      </c>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr"/>
       <c r="F483" t="n">
@@ -12107,7 +12111,11 @@
           <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr"/>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>$-49.7B</t>
+        </is>
+      </c>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="n">
@@ -12125,7 +12133,11 @@
           <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr"/>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>$72B</t>
+        </is>
+      </c>
       <c r="D485" t="inlineStr">
         <is>
           <t>$149.1B</t>
@@ -12144,22 +12156,14 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>$72B</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+          <t>Foreign Bond InvestmentDEC</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="487">
@@ -12170,14 +12174,10 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>$-49.7B</t>
-        </is>
-      </c>
+          <t>Overall Net Capital FlowsDEC</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
@@ -12192,18 +12192,18 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>$87.1B</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr"/>
+          <t>Net Long-term TIC FlowsDEC</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -12217,11 +12217,7 @@
           <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
@@ -12236,18 +12232,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -12258,14 +12250,10 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
@@ -12280,18 +12268,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12302,14 +12286,10 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12324,10 +12304,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr"/>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
@@ -12342,14 +12326,18 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12360,10 +12348,14 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
@@ -12381,7 +12373,11 @@
           <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr"/>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
@@ -12396,14 +12392,18 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -12414,18 +12414,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -12436,18 +12440,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr"/>
+          <t>Housing StartsJAN</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>1.366M</t>
+        </is>
+      </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12465,11 +12473,7 @@
           <t>Housing Starts MoMJAN</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
+      <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
@@ -12488,22 +12492,26 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -12514,26 +12522,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12544,22 +12548,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>Building Permits MoM PrelJAN</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -12570,18 +12574,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -12592,26 +12600,18 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>Building Permits MoM PrelJAN</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
@@ -12774,16 +12774,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr"/>
-      <c r="E515" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E515" t="inlineStr"/>
       <c r="F515" t="n">
         <v>3</v>
       </c>
@@ -12796,7 +12792,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
@@ -12814,18 +12810,18 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F517" t="n">
@@ -12840,12 +12836,20 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr"/>
-      <c r="E518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F518" t="n">
         <v>3</v>
       </c>
@@ -12876,20 +12880,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E520" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr"/>
       <c r="F520" t="n">
         <v>3</v>
       </c>
@@ -12902,18 +12898,18 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F521" t="n">
@@ -12928,12 +12924,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr"/>
-      <c r="E522" t="inlineStr"/>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F522" t="n">
         <v>3</v>
       </c>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
@@ -13044,7 +13044,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
@@ -13062,14 +13062,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13134,14 +13134,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13368,18 +13368,14 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F546" t="n">
@@ -13394,18 +13390,18 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -13420,11 +13416,15 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -13468,14 +13468,18 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F550" t="n">
@@ -13490,22 +13494,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -13516,18 +13516,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F552" t="n">
@@ -13542,18 +13542,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13568,18 +13568,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F554" t="n">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F555" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="556">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13942,14 +13942,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F573" t="n">
@@ -13964,18 +13964,14 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F574" t="n">
@@ -14012,18 +14008,22 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F576" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -14034,22 +14034,18 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -14060,14 +14056,18 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F578" t="n">
@@ -14082,14 +14082,14 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -14104,22 +14104,18 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F580" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="581">
@@ -14130,14 +14126,14 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -14152,18 +14148,22 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F582" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="583">
@@ -14174,22 +14174,18 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F583" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="584">
@@ -14200,14 +14196,14 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F584" t="n">
@@ -14244,22 +14240,18 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F586" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="587">
@@ -14270,22 +14262,22 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F587" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="588">
@@ -14296,18 +14288,22 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F588" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="589">
@@ -14344,7 +14340,11 @@
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>-1</t>
@@ -14362,14 +14362,14 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14406,14 +14406,14 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr"/>
       <c r="E593" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -14522,7 +14522,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14558,14 +14558,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14576,14 +14576,14 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -14630,14 +14630,14 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14720,7 +14720,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14738,14 +14738,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="612">
@@ -14756,14 +14756,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="613">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14828,14 +14828,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="617">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -15122,14 +15122,14 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr"/>
       <c r="F631" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="632">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15176,14 +15176,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr"/>
       <c r="F634" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -15212,14 +15212,14 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr"/>
       <c r="F636" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="637">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15248,14 +15248,14 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr"/>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15374,7 +15374,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15518,12 +15518,16 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
-      <c r="E653" t="inlineStr"/>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F653" t="n">
         <v>3</v>
       </c>
@@ -15536,14 +15540,18 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr"/>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="F654" t="n">
@@ -15558,20 +15566,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E655" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D655" t="inlineStr"/>
+      <c r="E655" t="inlineStr"/>
       <c r="F655" t="n">
         <v>3</v>
       </c>
@@ -15584,12 +15584,20 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
-      <c r="D656" t="inlineStr"/>
-      <c r="E656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F656" t="n">
         <v>3</v>
       </c>
@@ -15602,20 +15610,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E657" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" t="inlineStr"/>
       <c r="F657" t="n">
         <v>3</v>
       </c>
@@ -15668,22 +15668,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F660" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="661">
@@ -15699,11 +15699,7 @@
       </c>
       <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr"/>
-      <c r="E661" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E661" t="inlineStr"/>
       <c r="F661" t="n">
         <v>3</v>
       </c>
@@ -15716,22 +15712,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F662" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663">
@@ -15742,22 +15738,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -15768,18 +15764,18 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -15794,22 +15790,18 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F665" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="666">
@@ -15820,22 +15812,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F666" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="667">
@@ -15846,14 +15838,18 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -15868,18 +15864,14 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D668" t="inlineStr"/>
       <c r="E668" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -15894,18 +15886,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
-      <c r="D669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F669" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670">
@@ -15916,22 +15912,22 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F670" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="671">
@@ -15968,18 +15964,22 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F672" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673">
@@ -15990,22 +15990,22 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F673" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -16016,18 +16016,22 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16038,18 +16042,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -16064,14 +16064,18 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -16086,18 +16090,14 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -16112,18 +16112,18 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -16138,14 +16138,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F679" t="n">
@@ -16160,22 +16160,18 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -16186,22 +16182,22 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -16212,22 +16208,22 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16238,12 +16234,20 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
-      <c r="E683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F683" t="n">
         <v>3</v>
       </c>
@@ -16256,18 +16260,18 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -16282,18 +16286,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -16308,16 +16308,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
         <v>2</v>
       </c>
@@ -16330,12 +16326,20 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
-      <c r="D687" t="inlineStr"/>
-      <c r="E687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="F687" t="n">
         <v>2</v>
       </c>
@@ -16348,20 +16352,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D688" t="inlineStr"/>
+      <c r="E688" t="inlineStr"/>
       <c r="F688" t="n">
         <v>2</v>
       </c>
@@ -16396,12 +16392,20 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
-      <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="F690" t="n">
         <v>2</v>
       </c>
@@ -16414,18 +16418,14 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
+      <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F691" t="n">
@@ -16440,15 +16440,11 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="n">
         <v>3</v>
@@ -16462,11 +16458,15 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr"/>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="n">
         <v>3</v>
@@ -16480,15 +16480,11 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="n">
         <v>3</v>
@@ -16502,11 +16498,15 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="n">
         <v>3</v>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16662,7 +16662,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16932,22 +16932,18 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F718" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="719">
@@ -16958,22 +16954,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E719" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D719" t="inlineStr"/>
+      <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -16984,22 +16972,18 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>$-114.7B</t>
-        </is>
-      </c>
+      <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F720" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="721">
@@ -17010,14 +16994,18 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
-      <c r="D721" t="inlineStr"/>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F721" t="n">
@@ -17032,18 +17020,14 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="E722" t="inlineStr"/>
       <c r="F722" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="723">
@@ -17054,18 +17038,18 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F723" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
@@ -17076,20 +17060,12 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
-      <c r="D724" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E724" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D724" t="inlineStr"/>
+      <c r="E724" t="inlineStr"/>
       <c r="F724" t="n">
         <v>2</v>
       </c>
@@ -17102,18 +17078,14 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr"/>
-      <c r="E725" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="E725" t="inlineStr"/>
       <c r="F725" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="726">
@@ -17124,22 +17096,18 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
-      <c r="D726" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F726" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="727">
@@ -17150,7 +17118,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -17172,7 +17140,11 @@
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E728" t="inlineStr">
         <is>
           <t>0.4%</t>
@@ -17190,22 +17162,22 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F729" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="730">
@@ -17220,8 +17192,16 @@
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
-      <c r="D730" t="inlineStr"/>
-      <c r="E730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F730" t="n">
         <v>1</v>
       </c>
@@ -17234,18 +17214,22 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
-      <c r="D731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F731" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="732">
@@ -17256,12 +17240,16 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
       <c r="D732" t="inlineStr"/>
-      <c r="E732" t="inlineStr"/>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F732" t="n">
         <v>2</v>
       </c>
@@ -17274,12 +17262,16 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr"/>
-      <c r="E733" t="inlineStr"/>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F733" t="n">
         <v>2</v>
       </c>
@@ -17297,7 +17289,11 @@
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr"/>
-      <c r="E734" t="inlineStr"/>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F734" t="n">
         <v>2</v>
       </c>
@@ -17310,18 +17306,22 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
-      <c r="D735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F735" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="736">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17508,14 +17508,14 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F744" t="n">
@@ -17552,18 +17552,18 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="747">
@@ -17574,18 +17574,18 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F747" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="748">
@@ -17618,14 +17618,14 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F749" t="n">
@@ -17640,18 +17640,18 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
       <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F750" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="751">
@@ -17662,14 +17662,14 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F751" t="n">
@@ -17684,18 +17684,18 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F752" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="753">
@@ -17706,18 +17706,18 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F753" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="754">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
@@ -17920,11 +17920,15 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
         <v>3</v>
@@ -17938,15 +17942,11 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D765" t="inlineStr"/>
       <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
         <v>3</v>
@@ -17988,6 +17988,96 @@
         <v>2</v>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>MBA Mortgage Market IndexFEB/28</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr"/>
+      <c r="D768" t="inlineStr"/>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr"/>
+      <c r="D769" t="inlineStr"/>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr"/>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr"/>
+      <c r="D771" t="inlineStr"/>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>MBA Purchase IndexFEB/28</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr"/>
+      <c r="D772" t="inlineStr"/>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F772"/>
+  <dimension ref="A1:F778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,22 +794,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -816,15 +816,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,18 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1608,18 +1608,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1634,18 +1638,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1660,22 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,26 +3174,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3204,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3230,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,22 +3252,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3282,18 +3282,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,18 +4348,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4370,22 +4374,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4396,18 +4396,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,19 +4422,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,18 +4604,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4660,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,22 +4682,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4728,18 +4712,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4754,12 +4742,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4776,26 +4764,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4806,26 +4786,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4836,18 +4816,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4858,12 +4846,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4880,22 +4868,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -4910,18 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4954,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4988,18 +4980,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5020,16 +5020,16 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5040,26 +5040,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5100,26 +5100,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -5266,22 +5266,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5292,26 +5296,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5322,18 +5322,18 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5348,22 +5348,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,22 +6198,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,22 +6242,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6272,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6294,18 +6290,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6474,22 +6474,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,18 +6530,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8572,26 +8572,14 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,22 +8590,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8620,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8650,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8688,18 +8680,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8714,22 +8710,18 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8744,22 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8774,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8804,12 +8796,20 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,26 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -8960,18 +8956,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8986,26 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9046,22 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,18 +9498,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,18 +9542,18 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="368">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,22 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,22 +9998,18 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -10024,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10046,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,18 +10064,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10090,19 +10090,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10116,18 +10112,22 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,14 +10396,14 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,14 +10450,14 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10902,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,22 +10924,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10950,22 +10950,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -11002,18 +10998,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11076,14 +11072,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11094,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,14 +11264,14 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -11286,18 +11286,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -11308,18 +11312,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11330,18 +11338,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -11382,14 +11386,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11404,14 +11412,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11426,22 +11434,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -12214,10 +12214,14 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
@@ -12232,14 +12236,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr"/>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12250,10 +12258,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
@@ -12268,14 +12280,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12286,10 +12302,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr"/>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12304,14 +12324,10 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
@@ -12326,18 +12342,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -12348,18 +12360,14 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12370,14 +12378,10 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
@@ -12392,14 +12396,10 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
@@ -12414,18 +12414,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12443,11 +12443,7 @@
           <t>Housing StartsJAN</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>1.366M</t>
-        </is>
-      </c>
+      <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
           <t>1.4M</t>
@@ -12470,18 +12466,26 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+          <t>Housing StartsJAN</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>1.366M</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -12492,26 +12496,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -12522,22 +12518,26 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -12548,18 +12548,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>Building Permits MoM PrelJAN</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12625,11 +12625,7 @@
           <t>Redbook YoYFEB/15</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>6.3%</t>
-        </is>
-      </c>
+      <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="n">
@@ -12647,7 +12643,11 @@
           <t>Redbook YoYFEB/15</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr"/>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr"/>
       <c r="F508" t="n">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
@@ -12792,12 +12792,16 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr"/>
-      <c r="E516" t="inlineStr"/>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F516" t="n">
         <v>3</v>
       </c>
@@ -12810,22 +12814,14 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr"/>
       <c r="F517" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="518">
@@ -12836,20 +12832,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr"/>
       <c r="F518" t="n">
         <v>3</v>
       </c>
@@ -12862,14 +12850,22 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
-      <c r="D519" t="inlineStr"/>
-      <c r="E519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F519" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="520">
@@ -12880,14 +12876,22 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr"/>
-      <c r="E520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F520" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="521">
@@ -12898,22 +12902,14 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E521" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr"/>
       <c r="F521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="522">
@@ -12924,16 +12920,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr"/>
-      <c r="E522" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E522" t="inlineStr"/>
       <c r="F522" t="n">
         <v>3</v>
       </c>
@@ -12946,12 +12938,20 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
-      <c r="D523" t="inlineStr"/>
-      <c r="E523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F523" t="n">
         <v>3</v>
       </c>
@@ -13062,14 +13062,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="530">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13134,14 +13134,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13224,14 +13224,14 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13260,14 +13260,14 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -13368,14 +13368,18 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F546" t="n">
@@ -13390,18 +13394,18 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -13416,15 +13420,11 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13942,18 +13942,22 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F573" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -13964,18 +13968,22 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F574" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="575">
@@ -13986,14 +13994,14 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F575" t="n">
@@ -14008,22 +14016,18 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F576" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="577">
@@ -14034,14 +14038,14 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -14104,14 +14108,14 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F580" t="n">
@@ -14126,14 +14130,14 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -14148,22 +14152,18 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F582" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="583">
@@ -14200,7 +14200,11 @@
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E584" t="inlineStr">
         <is>
           <t>-1</t>
@@ -14218,18 +14222,22 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
-      <c r="D585" t="inlineStr"/>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F585" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="586">
@@ -14262,22 +14270,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F587" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="588">
@@ -14314,14 +14318,18 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14336,18 +14344,14 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -14406,14 +14410,14 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr"/>
       <c r="E593" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -14428,14 +14432,14 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -14504,14 +14508,14 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14522,7 +14526,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14540,14 +14544,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14558,14 +14562,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14576,14 +14580,14 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14630,14 +14634,14 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -14648,7 +14652,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14666,7 +14670,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14684,7 +14688,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14702,7 +14706,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14720,7 +14724,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14738,7 +14742,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14756,14 +14760,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
@@ -14774,14 +14778,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14792,7 +14796,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14810,7 +14814,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14828,14 +14832,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
@@ -14882,18 +14886,14 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
+      <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F619" t="n">
@@ -14908,14 +14908,18 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -15014,7 +15018,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -15032,7 +15036,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -15050,7 +15054,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15068,7 +15072,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15086,14 +15090,14 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr"/>
       <c r="E629" t="inlineStr"/>
       <c r="F629" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="630">
@@ -15104,7 +15108,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -15140,7 +15144,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15176,14 +15180,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr"/>
       <c r="F634" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="635">
@@ -15194,14 +15198,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15212,14 +15216,14 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr"/>
       <c r="F636" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="637">
@@ -15230,7 +15234,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15248,7 +15252,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
@@ -15266,7 +15270,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15284,14 +15288,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -15302,14 +15306,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
       <c r="F641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -15338,14 +15342,14 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr"/>
       <c r="F643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -15356,14 +15360,14 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr"/>
       <c r="F644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -15446,7 +15450,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15464,7 +15468,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15518,14 +15522,18 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -15540,20 +15548,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D654" t="inlineStr"/>
+      <c r="E654" t="inlineStr"/>
       <c r="F654" t="n">
         <v>3</v>
       </c>
@@ -15566,12 +15566,16 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr"/>
-      <c r="E655" t="inlineStr"/>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F655" t="n">
         <v>3</v>
       </c>
@@ -15584,18 +15588,14 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
-      <c r="D656" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F656" t="n">
@@ -15610,7 +15610,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15628,14 +15628,18 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
-      <c r="D658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="F658" t="n">
@@ -15668,22 +15672,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F660" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="661">
@@ -15694,12 +15698,20 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
-      <c r="D661" t="inlineStr"/>
-      <c r="E661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F661" t="n">
         <v>3</v>
       </c>
@@ -15712,22 +15724,18 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F662" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="663">
@@ -15738,22 +15746,18 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
-      <c r="D663" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664">
@@ -15764,22 +15768,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F664" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="665">
@@ -15790,14 +15794,18 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr"/>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -15812,18 +15820,14 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D666" t="inlineStr"/>
       <c r="E666" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -15838,22 +15842,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F667" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="668">
@@ -15864,18 +15868,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr"/>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F668" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="669">
@@ -15886,22 +15894,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F669" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="670">
@@ -15964,22 +15972,18 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F672" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="673">
@@ -15990,18 +15994,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -16016,22 +16020,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F674" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -16042,18 +16042,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr"/>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F675" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="676">
@@ -16064,18 +16068,14 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -16090,18 +16090,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr"/>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F677" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678">
@@ -16112,18 +16116,18 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -16138,14 +16142,18 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr"/>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F679" t="n">
@@ -16160,18 +16168,22 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F680" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681">
@@ -16182,18 +16194,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F681" t="n">
@@ -16208,18 +16216,18 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -16234,22 +16242,22 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -16260,18 +16268,14 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -16286,14 +16290,18 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -16326,18 +16334,14 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
-      <c r="D687" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
+      <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F687" t="n">
@@ -16352,12 +16356,20 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr"/>
-      <c r="E688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="F688" t="n">
         <v>2</v>
       </c>
@@ -16370,14 +16382,18 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
-      <c r="D689" t="inlineStr"/>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F689" t="n">
@@ -16392,18 +16408,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
-      <c r="D690" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
+      <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F690" t="n">
@@ -16418,16 +16430,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr"/>
-      <c r="E691" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="E691" t="inlineStr"/>
       <c r="F691" t="n">
         <v>2</v>
       </c>
@@ -16440,11 +16448,15 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="n">
         <v>3</v>
@@ -16458,15 +16470,11 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="n">
         <v>3</v>
@@ -16480,11 +16488,15 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="n">
         <v>3</v>
@@ -16498,15 +16510,11 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D695" t="inlineStr"/>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="n">
         <v>3</v>
@@ -16542,7 +16550,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16586,7 +16594,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16734,7 +16742,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -16752,7 +16760,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16932,18 +16940,22 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F718" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="719">
@@ -16954,12 +16966,20 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr"/>
-      <c r="E719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>$ -116.0B</t>
+        </is>
+      </c>
       <c r="F719" t="n">
         <v>2</v>
       </c>
@@ -16972,14 +16992,18 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F720" t="n">
@@ -16994,22 +17018,22 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F721" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="722">
@@ -17020,12 +17044,20 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F722" t="n">
         <v>1</v>
       </c>
@@ -17038,18 +17070,18 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F723" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="724">
@@ -17060,14 +17092,18 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr"/>
-      <c r="E724" t="inlineStr"/>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F724" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="725">
@@ -17078,12 +17114,16 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr"/>
-      <c r="E725" t="inlineStr"/>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F725" t="n">
         <v>2</v>
       </c>
@@ -17096,18 +17136,18 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F726" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="727">
@@ -17118,14 +17158,18 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr"/>
-      <c r="E727" t="inlineStr"/>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F727" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="728">
@@ -17162,22 +17206,22 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F729" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="730">
@@ -17188,13 +17232,13 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -17214,22 +17258,22 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F731" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="732">
@@ -17240,14 +17284,18 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
-      <c r="D732" t="inlineStr"/>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F732" t="n">
@@ -17262,14 +17310,14 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F733" t="n">
@@ -17284,14 +17332,14 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F734" t="n">
@@ -17306,18 +17354,14 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
-      <c r="D735" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F735" t="n">
@@ -17508,14 +17552,14 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F744" t="n">
@@ -17552,14 +17596,14 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F746" t="n">
@@ -17574,18 +17618,18 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F747" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="748">
@@ -17596,14 +17640,14 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F748" t="n">
@@ -17618,14 +17662,14 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F749" t="n">
@@ -17662,18 +17706,18 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F751" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="752">
@@ -17684,18 +17728,18 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F752" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="753">
@@ -17706,18 +17750,18 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F753" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="754">
@@ -17746,7 +17790,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -17782,7 +17826,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
@@ -17880,15 +17924,11 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
         <v>3</v>
@@ -17942,11 +17982,15 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
         <v>3</v>
@@ -17996,7 +18040,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -18014,14 +18058,14 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr"/>
       <c r="F769" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="770">
@@ -18050,14 +18094,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="772">
@@ -18078,6 +18122,118 @@
         <v>3</v>
       </c>
     </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>MBA Purchase IndexFEB/28</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr"/>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>MBA Mortgage Market IndexFEB/28</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr"/>
+      <c r="D774" t="inlineStr"/>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr"/>
+      <c r="D775" t="inlineStr"/>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr"/>
+      <c r="D776" t="inlineStr"/>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2025-03-05 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr"/>
+      <c r="D777" t="inlineStr"/>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2025-03-05 18:45:00+05:30</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>ADP Employment ChangeFEB</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr"/>
+      <c r="D778" t="inlineStr"/>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>200.0K</t>
+        </is>
+      </c>
+      <c r="F778" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F778"/>
+  <dimension ref="A1:F779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,22 +746,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -772,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -794,18 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -816,19 +816,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -842,18 +838,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -864,15 +864,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1608,22 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,22 +3226,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3252,26 +3256,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3282,18 +3282,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4096,22 +4096,18 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,22 +4122,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4156,18 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,19 +4300,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,18 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4348,22 +4348,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4422,15 +4414,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,18 +4462,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,18 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4630,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4660,18 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4682,7 +4698,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4692,16 +4708,16 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4712,22 +4728,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4742,12 +4754,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4764,18 +4776,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4786,22 +4806,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4816,26 +4836,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4846,12 +4858,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4868,18 +4880,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -4894,26 +4910,18 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -4954,18 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4980,26 +4988,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5010,26 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5040,26 +5040,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5100,26 +5100,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -5266,22 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5296,18 +5296,18 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5322,22 +5322,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5348,26 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,22 +6242,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,22 +6290,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6316,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,22 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6408,18 +6404,22 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -6474,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6530,22 +6534,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,26 +7066,22 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7092,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,22 +7122,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,22 +8350,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8380,18 +8376,22 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,12 +8572,20 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8590,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8620,22 +8628,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8650,22 +8658,18 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8680,26 +8684,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8710,22 +8714,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8736,26 +8744,14 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8766,26 +8762,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -8796,18 +8792,22 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8852,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8878,15 +8874,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8956,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8986,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,18 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9042,26 +9046,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,18 +9498,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,18 +9542,18 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,19 +9950,15 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>3</v>
@@ -9976,18 +9972,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,18 +10020,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10042,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10068,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,12 +10094,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10112,22 +10116,18 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,14 +10450,14 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,14 +10880,18 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10906,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,18 +10928,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
@@ -10972,22 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,18 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,14 +11072,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11094,22 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,14 +11264,14 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -11286,22 +11286,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11312,22 +11308,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11338,14 +11330,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -11386,18 +11382,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11412,18 +11404,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11430,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11456,14 +11456,14 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -12214,14 +12214,10 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
@@ -12236,14 +12232,10 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
@@ -12258,18 +12250,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12280,18 +12268,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12302,14 +12286,10 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12324,14 +12304,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12342,10 +12326,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
@@ -12360,14 +12348,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr"/>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -12378,10 +12370,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
@@ -12396,10 +12392,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr"/>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
@@ -12414,22 +12414,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>Building Permits MoM PrelJAN</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12440,18 +12440,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12469,11 +12469,7 @@
           <t>Housing StartsJAN</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>1.366M</t>
-        </is>
-      </c>
+      <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
           <t>1.4M</t>
@@ -12496,18 +12492,26 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+          <t>Housing StartsJAN</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>1.366M</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -12518,26 +12522,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12548,22 +12544,26 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -12574,18 +12574,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12625,7 +12625,11 @@
           <t>Redbook YoYFEB/15</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="n">
@@ -12643,11 +12647,7 @@
           <t>Redbook YoYFEB/15</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>6.3%</t>
-        </is>
-      </c>
+      <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr"/>
       <c r="F508" t="n">
@@ -12774,12 +12774,20 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
-      <c r="D515" t="inlineStr"/>
-      <c r="E515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F515" t="n">
         <v>3</v>
       </c>
@@ -12792,16 +12800,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr"/>
-      <c r="E516" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E516" t="inlineStr"/>
       <c r="F516" t="n">
         <v>3</v>
       </c>
@@ -12814,14 +12818,22 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr"/>
-      <c r="E517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F517" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
@@ -12832,14 +12844,22 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr"/>
-      <c r="E518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F518" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="519">
@@ -12850,22 +12870,14 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr"/>
       <c r="F519" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="520">
@@ -12876,22 +12888,14 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E520" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr"/>
       <c r="F520" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="521">
@@ -12902,12 +12906,16 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr"/>
-      <c r="E521" t="inlineStr"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F521" t="n">
         <v>3</v>
       </c>
@@ -12920,7 +12928,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -12938,20 +12946,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E523" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr"/>
       <c r="F523" t="n">
         <v>3</v>
       </c>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -13080,14 +13080,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13134,14 +13134,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,14 +13188,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13260,14 +13260,14 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -13368,18 +13368,18 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F546" t="n">
@@ -13394,15 +13394,11 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -13420,14 +13416,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13968,22 +13968,18 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -14038,14 +14034,14 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -14108,18 +14104,22 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F580" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="581">
@@ -14130,14 +14130,18 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -14152,14 +14156,14 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F582" t="n">
@@ -14270,14 +14274,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14318,18 +14326,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14366,14 +14370,14 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14388,14 +14392,14 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -14508,14 +14512,14 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -14580,14 +14584,14 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -14706,14 +14710,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="610">
@@ -14724,7 +14728,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14742,7 +14746,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14778,14 +14782,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614">
@@ -14796,7 +14800,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14814,7 +14818,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14934,7 +14938,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -14952,7 +14956,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
@@ -15018,7 +15022,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -15036,7 +15040,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -15054,7 +15058,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15072,7 +15076,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15090,14 +15094,14 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr"/>
       <c r="E629" t="inlineStr"/>
       <c r="F629" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="630">
@@ -15108,14 +15112,14 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr"/>
       <c r="F630" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="631">
@@ -15144,7 +15148,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15162,7 +15166,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15180,7 +15184,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15198,7 +15202,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -15216,7 +15220,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15234,14 +15238,14 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr"/>
       <c r="F637" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638">
@@ -15270,14 +15274,14 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -15288,14 +15292,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15306,14 +15310,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
       <c r="F641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -15522,18 +15526,14 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -15548,12 +15548,20 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr"/>
-      <c r="E654" t="inlineStr"/>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F654" t="n">
         <v>3</v>
       </c>
@@ -15566,16 +15574,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr"/>
-      <c r="E655" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E655" t="inlineStr"/>
       <c r="F655" t="n">
         <v>3</v>
       </c>
@@ -15610,12 +15614,20 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr"/>
-      <c r="E657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F657" t="n">
         <v>3</v>
       </c>
@@ -15628,20 +15640,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
-      <c r="D658" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E658" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D658" t="inlineStr"/>
+      <c r="E658" t="inlineStr"/>
       <c r="F658" t="n">
         <v>3</v>
       </c>
@@ -15654,7 +15658,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15698,18 +15702,14 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
-      <c r="D661" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -15724,14 +15724,18 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr"/>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F662" t="n">
@@ -15746,14 +15750,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -15768,18 +15772,14 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
-      <c r="D664" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -15794,18 +15794,18 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -15820,14 +15820,18 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -15842,22 +15846,18 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D667" t="inlineStr"/>
       <c r="E667" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F667" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="668">
@@ -15868,18 +15868,18 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -15894,18 +15894,18 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F669" t="n">
@@ -15920,22 +15920,22 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F670" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671">
@@ -15946,18 +15946,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -15972,14 +15972,14 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F672" t="n">
@@ -15994,22 +15994,22 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F673" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="674">
@@ -16020,18 +16020,22 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16042,22 +16046,18 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
+      <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F675" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16068,18 +16068,22 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F676" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="677">
@@ -16090,22 +16094,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F677" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="678">
@@ -16116,22 +16120,22 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F678" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="679">
@@ -16142,18 +16146,18 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F679" t="n">
@@ -16168,22 +16172,22 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F680" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -16194,18 +16198,22 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="682">
@@ -16216,18 +16224,18 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -16242,22 +16250,18 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -16268,18 +16272,22 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
@@ -16290,18 +16298,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -16382,20 +16386,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
-      <c r="D689" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E689" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D689" t="inlineStr"/>
+      <c r="E689" t="inlineStr"/>
       <c r="F689" t="n">
         <v>2</v>
       </c>
@@ -16430,12 +16426,20 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr"/>
-      <c r="E691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="F691" t="n">
         <v>2</v>
       </c>
@@ -16448,15 +16452,11 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="n">
         <v>3</v>
@@ -16470,11 +16470,15 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr"/>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="n">
         <v>3</v>
@@ -16488,15 +16492,11 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="n">
         <v>3</v>
@@ -16510,11 +16510,15 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="n">
         <v>3</v>
@@ -16550,7 +16554,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16572,7 +16576,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16724,7 +16728,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16742,7 +16746,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -16940,18 +16944,14 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr">
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr">
         <is>
           <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>0.2%</t>
         </is>
       </c>
       <c r="F718" t="n">
@@ -16966,22 +16966,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F719" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
@@ -16992,13 +16992,13 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -17018,13 +17018,13 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -17044,22 +17044,22 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F722" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="723">
@@ -17136,14 +17136,14 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F726" t="n">
@@ -17180,22 +17180,22 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F728" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="729">
@@ -17284,22 +17284,22 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
       <c r="D732" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F732" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="733">
@@ -17354,14 +17354,18 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
-      <c r="D735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F735" t="n">
@@ -17428,7 +17432,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17446,7 +17450,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17464,7 +17468,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17482,7 +17486,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -17552,18 +17556,18 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F744" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="745">
@@ -17574,18 +17578,18 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F745" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="746">
@@ -17596,18 +17600,18 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="747">
@@ -17618,14 +17622,14 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F747" t="n">
@@ -17640,14 +17644,14 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F748" t="n">
@@ -17662,14 +17666,14 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F749" t="n">
@@ -17706,18 +17710,18 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F751" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="752">
@@ -17728,18 +17732,18 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F752" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="753">
@@ -17750,18 +17754,18 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F753" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="754">
@@ -17790,7 +17794,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -17826,7 +17830,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
@@ -17924,11 +17928,15 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr"/>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
         <v>3</v>
@@ -17942,11 +17950,15 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
         <v>3</v>
@@ -17960,15 +17972,11 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
         <v>3</v>
@@ -17982,15 +17990,11 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D765" t="inlineStr"/>
       <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
         <v>3</v>
@@ -18058,14 +18062,14 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr"/>
       <c r="F769" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="770">
@@ -18094,14 +18098,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="772">
@@ -18130,14 +18134,14 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="774">
@@ -18148,7 +18152,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
@@ -18184,7 +18188,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -18202,14 +18206,14 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
       <c r="D777" t="inlineStr"/>
       <c r="E777" t="inlineStr"/>
       <c r="F777" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="778">
@@ -18231,6 +18235,28 @@
         </is>
       </c>
       <c r="F778" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2025-03-05 18:45:00+05:30</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>ADP Employment ChangeFEB</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr"/>
+      <c r="D779" t="inlineStr"/>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>200.0K</t>
+        </is>
+      </c>
+      <c r="F779" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -746,17 +746,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -772,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -794,12 +794,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -816,15 +816,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,18 +908,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1088,26 +1088,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1118,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1144,26 +1148,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1174,26 +1174,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1424,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1450,26 +1454,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1712,22 +1712,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1738,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1768,18 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1794,26 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1824,22 +1828,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2124,18 +2124,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2150,12 +2154,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>Initial Jobless ClaimsJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>201K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>218K</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="F71" t="n">
         <v>2</v>
       </c>
@@ -2168,22 +2184,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2198,24 +2210,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
         <v>2</v>
       </c>
@@ -2228,22 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2332,22 +2332,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2380,12 +2376,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2402,15 +2398,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2494,18 +2494,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2516,19 +2520,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>3</v>
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3588,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3626,14 +3626,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,18 +3644,18 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,12 +3670,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3689,11 +3685,11 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3704,18 +3700,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,22 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,18 +3926,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,18 +4014,18 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,19 +4300,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,22 +4322,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4352,18 +4344,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4374,15 +4370,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>3</v>
@@ -4396,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4422,18 +4418,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,18 +4612,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4626,22 +4642,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4656,17 +4672,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4675,7 +4691,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4686,16 +4702,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4708,24 +4728,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4738,18 +4750,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -4760,26 +4780,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4790,18 +4806,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4816,26 +4832,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4846,16 +4854,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,20 +4884,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4894,17 +4906,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -4913,7 +4925,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4924,22 +4936,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4954,20 +4966,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
         <v>3</v>
       </c>
@@ -4980,26 +4988,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5010,22 +5010,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/16</t>
+          <t>30-Year Mortgage RateJAN/16</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>7.04%</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/16</t>
+          <t>15-Year Mortgage RateJAN/16</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,18 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6220,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,22 +6246,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,22 +6386,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>4.24M</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6616,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6646,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6676,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7204,18 +7204,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7230,18 +7230,22 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7256,26 +7260,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7286,22 +7286,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7316,22 +7312,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -7528,12 +7528,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -7816,22 +7816,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7842,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,19 +7886,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7912,15 +7908,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7956,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,17 +7978,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,26 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8126,18 +8126,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8182,18 +8182,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8208,26 +8208,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8238,22 +8234,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -8264,26 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8294,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,22 +8320,26 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8572,24 +8572,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8602,18 +8590,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,22 +8620,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8654,22 +8650,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8684,26 +8680,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -8714,26 +8710,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8744,26 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8774,22 +8762,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8804,14 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+          <t>Personal Spending MoMDEC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,18 +9498,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9820,18 +9820,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,18 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,22 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,15 +10020,19 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>3</v>
@@ -10042,22 +10046,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -10468,18 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,22 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -10520,22 +10516,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10546,18 +10542,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -10568,18 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,18 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -10902,22 +10906,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -10928,22 +10932,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10954,14 +10954,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10976,14 +10976,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,14 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11020,18 +11024,14 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,18 +11046,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11068,22 +11072,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11094,22 +11098,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,14 +11264,14 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -11286,14 +11286,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -11308,13 +11308,13 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -11334,22 +11334,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -11360,14 +11360,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F450" t="n">
@@ -11382,22 +11386,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11408,14 +11412,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11430,22 +11434,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -12006,14 +12006,10 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>4.270%</t>
-        </is>
-      </c>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="n">
@@ -12028,18 +12024,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -12050,10 +12042,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr"/>
+          <t>42-Day Bill Auction</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>4.270%</t>
+        </is>
+      </c>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
@@ -12068,14 +12064,18 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr"/>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="483">
@@ -12214,18 +12214,14 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="490">
@@ -12236,14 +12232,10 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
@@ -12258,18 +12250,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12280,14 +12268,10 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
@@ -12302,14 +12286,10 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12324,10 +12304,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
@@ -12342,14 +12326,18 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr"/>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -12363,7 +12351,11 @@
           <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr"/>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
@@ -12378,14 +12370,18 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12399,7 +12395,11 @@
           <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr"/>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
@@ -12414,22 +12414,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.366M</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12444,18 +12444,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501">
@@ -12466,18 +12470,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12492,18 +12496,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -12514,22 +12522,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12543,11 +12551,7 @@
           <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
@@ -12566,18 +12570,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr"/>
+          <t>Building Permits PrelJAN</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12592,26 +12600,18 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13368,11 +13368,15 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -13390,18 +13394,14 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -13416,18 +13416,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13942,18 +13942,22 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F573" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -14060,22 +14064,18 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F578" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="579">
@@ -14086,18 +14086,14 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -14156,14 +14152,18 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F582" t="n">
@@ -14274,22 +14274,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F587" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="588">
@@ -14300,18 +14296,14 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -14326,14 +14318,18 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14348,18 +14344,22 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F590" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591">
@@ -14548,14 +14548,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14566,14 +14566,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15184,14 +15184,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr"/>
       <c r="F634" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15346,14 +15346,14 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr"/>
       <c r="F643" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15526,12 +15526,20 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
-      <c r="E653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F653" t="n">
         <v>3</v>
       </c>
@@ -15610,20 +15618,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E657" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" t="inlineStr"/>
       <c r="F657" t="n">
         <v>3</v>
       </c>
@@ -15998,18 +15998,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -16024,22 +16024,22 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F674" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -16050,18 +16050,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr"/>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F675" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="676">
@@ -16072,18 +16076,14 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -16098,18 +16098,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr"/>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F677" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678">
@@ -16120,22 +16124,22 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F678" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="679">
@@ -16146,18 +16150,22 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr"/>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -16168,22 +16176,18 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -16194,22 +16198,18 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr">
+      <c r="D681" t="inlineStr"/>
+      <c r="E681" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E681" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -16220,18 +16220,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -16246,22 +16242,22 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -16272,14 +16268,18 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -16294,18 +16294,18 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -16452,11 +16452,15 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="n">
         <v>3</v>
@@ -16510,15 +16514,11 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D695" t="inlineStr"/>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="n">
         <v>3</v>
@@ -17118,18 +17118,14 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
-      <c r="D725" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F725" t="n">
@@ -17166,18 +17162,22 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F727" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="728">
@@ -17188,14 +17188,18 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F728" t="n">
@@ -17210,18 +17214,22 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
-      <c r="D729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F729" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="730">
@@ -17232,22 +17240,22 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F730" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="731">
@@ -17258,18 +17266,22 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
-      <c r="D731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F731" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="732">
@@ -17280,18 +17292,14 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
-      <c r="D732" t="inlineStr">
-        <is>
-          <t>$-114.7B</t>
-        </is>
-      </c>
+      <c r="D732" t="inlineStr"/>
       <c r="E732" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F732" t="n">
@@ -17306,22 +17314,18 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
-      <c r="D733" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F733" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="734">
@@ -17332,22 +17336,18 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
-      <c r="D734" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F734" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="735">
@@ -17578,18 +17578,18 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F745" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="746">
@@ -17600,18 +17600,18 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="747">
@@ -17644,18 +17644,18 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F748" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749">
@@ -17754,18 +17754,18 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F753" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="754">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
@@ -18080,14 +18080,14 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr"/>
       <c r="F770" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="771">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -18170,14 +18170,14 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
       <c r="D775" t="inlineStr"/>
       <c r="E775" t="inlineStr"/>
       <c r="F775" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="776">
@@ -18532,14 +18532,14 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C792" t="inlineStr"/>
       <c r="D792" t="inlineStr"/>
       <c r="E792" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="F792" t="n">
@@ -18554,12 +18554,16 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr"/>
-      <c r="E793" t="inlineStr"/>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F793" t="n">
         <v>3</v>
       </c>
@@ -18572,16 +18576,12 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="inlineStr"/>
-      <c r="E794" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
+      <c r="E794" t="inlineStr"/>
       <c r="F794" t="n">
         <v>3</v>
       </c>
@@ -18594,14 +18594,14 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
       <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="F795" t="n">
@@ -18616,14 +18616,14 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
       <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="F796" t="n">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
@@ -18808,14 +18808,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="807">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
@@ -18862,14 +18862,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="810">
@@ -18898,14 +18898,14 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr"/>
       <c r="F811" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="812">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
@@ -18952,14 +18952,14 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C814" t="inlineStr"/>
       <c r="D814" t="inlineStr"/>
       <c r="E814" t="inlineStr"/>
       <c r="F814" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="815">
